--- a/examples/demos/09_tail_risk_op_losses.xlsx
+++ b/examples/demos/09_tail_risk_op_losses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F44E6AB-371E-4BB7-B3B3-99BDA49B0648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21C7ACB-7EBC-4882-9A77-D0272E5DF3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Demo 09 — Tail risk: GPD tails and operational-risk capital</t>
   </si>
@@ -42,22 +42,40 @@
     <t>Tools demonstrated: fit_and_rank_distributions, fit_tail, compute_distribution, create_aggregate_mc, wrap_with_output, run_simulation, get_tail_risk</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/09_tail_risk_op_losses.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 09_tail_risk_op_losses.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Using this workbook: fit distributions to all losses in 'Data'!B5:B424 and rank them; fit a GPD tail to the exceedances in 'Data'!D5:D44 and write the fitted object into Model!B6, reporting the tail's P99 and P99.9 analytically; build an annual aggregate in Model!B11 (frequency VosePoisson(60), severity = the best-fit body distribution, Monte Carlo method); write =B11 into Model!B13 wrapped as output "OpLoss"; run 10,000 iterations; and give me the 99.9% VaR and CVaR of OpLoss — the capital requirement.</t>
+  </si>
+  <si>
+    <t>Expected: body fit + GPD tail + a simulated 99.9% capital number, in one pass.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
   </si>
   <si>
-    <t>Open the workbook in Excel (see PREREQUISITES above). Look at the 'Data' sheet: 420 loss events in B5:B424, and their exceedances over a $150k threshold in column D.</t>
+    <t>Open the workbook in Excel (see GETTING STARTED above). Look at the 'Data' sheet: 420 loss events in B5:B424, and their exceedances over a $150k threshold in column D.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Open 09_tail_risk_op_losses.xlsx from the demo folder.</t>
   </si>
   <si>
     <t>Expected: The workbook opens; Data holds the loss history, Model holds the yellow cells Claude will fill.</t>
@@ -199,13 +217,53 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -254,12 +312,42 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -304,32 +392,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -638,7 +739,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -646,233 +747,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="12"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="16"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="12"/>
-    </row>
-    <row r="15" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="16"/>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="11">
         <v>1</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
+      <c r="B21" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="11">
         <v>2</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3">
+      <c r="B25" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="11">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3">
+      <c r="B29" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="11">
         <v>4</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3">
+      <c r="B33" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="11">
         <v>5</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="3">
+      <c r="B37" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="11">
         <v>6</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="12"/>
-    </row>
-    <row r="40" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="4" t="s">
+      <c r="B41" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="11" t="s">
+    <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="12"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="1" t="s">
+    </row>
+    <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="6"/>
-      <c r="B46" s="1" t="s">
+    <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A47" s="7"/>
-      <c r="B47" s="1" t="s">
+      <c r="B45" s="16"/>
+    </row>
+    <row r="46" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" s="2"/>
-      <c r="B48" s="1" t="s">
+    <row r="47" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="8" t="s">
         <v>36</v>
       </c>
     </row>
+    <row r="48" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="16"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="12"/>
+      <c r="B51" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="13"/>
+      <c r="B52" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A53" s="14"/>
+      <c r="B53" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" s="9"/>
+      <c r="B54" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A44:B44"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A45:B45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -894,62 +1022,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="A1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="A2" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>41</v>
+      <c r="A4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="6">
         <v>25.1</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="6">
         <v>95.3</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
+      <c r="F5" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="6">
         <v>50.1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="6">
         <v>34.4</v>
       </c>
     </row>
@@ -957,10 +1085,10 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>71.900000000000006</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>3.9</v>
       </c>
     </row>
@@ -968,24 +1096,24 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="6">
         <v>13.7</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="6">
         <v>87.5</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>43</v>
+      <c r="F8" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>5</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>85.1</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>170.1</v>
       </c>
     </row>
@@ -993,10 +1121,10 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <v>49.7</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <v>95.3</v>
       </c>
     </row>
@@ -1004,10 +1132,10 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <v>86.5</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6">
         <v>76</v>
       </c>
     </row>
@@ -1015,10 +1143,10 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <v>50.6</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <v>78.2</v>
       </c>
     </row>
@@ -1026,10 +1154,10 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="6">
         <v>128.69999999999999</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="6">
         <v>297</v>
       </c>
     </row>
@@ -1037,10 +1165,10 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="6">
         <v>14.2</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="6">
         <v>51</v>
       </c>
     </row>
@@ -1048,10 +1176,10 @@
       <c r="A15">
         <v>11</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="6">
         <v>245.3</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="6">
         <v>7.8</v>
       </c>
     </row>
@@ -1059,10 +1187,10 @@
       <c r="A16">
         <v>12</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <v>134.30000000000001</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="6">
         <v>216.3</v>
       </c>
     </row>
@@ -1070,10 +1198,10 @@
       <c r="A17">
         <v>13</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="6">
         <v>20.2</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="6">
         <v>98.1</v>
       </c>
     </row>
@@ -1081,10 +1209,10 @@
       <c r="A18">
         <v>14</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="6">
         <v>76</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="6">
         <v>22.6</v>
       </c>
     </row>
@@ -1092,10 +1220,10 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="6">
         <v>60.6</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="6">
         <v>18.600000000000001</v>
       </c>
     </row>
@@ -1103,10 +1231,10 @@
       <c r="A20">
         <v>16</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="6">
         <v>6.1</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="6">
         <v>107.6</v>
       </c>
     </row>
@@ -1114,10 +1242,10 @@
       <c r="A21">
         <v>17</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="6">
         <v>71</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="6">
         <v>32.700000000000003</v>
       </c>
     </row>
@@ -1125,10 +1253,10 @@
       <c r="A22">
         <v>18</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="6">
         <v>20.6</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="6">
         <v>28.2</v>
       </c>
     </row>
@@ -1136,10 +1264,10 @@
       <c r="A23">
         <v>19</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="6">
         <v>29.2</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="6">
         <v>128.5</v>
       </c>
     </row>
@@ -1147,10 +1275,10 @@
       <c r="A24">
         <v>20</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="6">
         <v>20.2</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="6">
         <v>154.30000000000001</v>
       </c>
     </row>
@@ -1158,10 +1286,10 @@
       <c r="A25">
         <v>21</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="6">
         <v>24.2</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="6">
         <v>31.4</v>
       </c>
     </row>
@@ -1169,10 +1297,10 @@
       <c r="A26">
         <v>22</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="6">
         <v>41</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="6">
         <v>15.5</v>
       </c>
     </row>
@@ -1180,10 +1308,10 @@
       <c r="A27">
         <v>23</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="6">
         <v>42.1</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="6">
         <v>37.9</v>
       </c>
     </row>
@@ -1191,10 +1319,10 @@
       <c r="A28">
         <v>24</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="6">
         <v>7.4</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="6">
         <v>19.8</v>
       </c>
     </row>
@@ -1202,10 +1330,10 @@
       <c r="A29">
         <v>25</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="6">
         <v>28.7</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="6">
         <v>6.2</v>
       </c>
     </row>
@@ -1213,10 +1341,10 @@
       <c r="A30">
         <v>26</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="6">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="6">
         <v>63.7</v>
       </c>
     </row>
@@ -1224,10 +1352,10 @@
       <c r="A31">
         <v>27</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="6">
         <v>10</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="6">
         <v>129.1</v>
       </c>
     </row>
@@ -1235,10 +1363,10 @@
       <c r="A32">
         <v>28</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="6">
         <v>26.4</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="6">
         <v>51.6</v>
       </c>
     </row>
@@ -1246,10 +1374,10 @@
       <c r="A33">
         <v>29</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="6">
         <v>93.3</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="6">
         <v>19.399999999999999</v>
       </c>
     </row>
@@ -1257,10 +1385,10 @@
       <c r="A34">
         <v>30</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="6">
         <v>73.7</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="6">
         <v>274.5</v>
       </c>
     </row>
@@ -1268,10 +1396,10 @@
       <c r="A35">
         <v>31</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="6">
         <v>146.69999999999999</v>
       </c>
     </row>
@@ -1279,10 +1407,10 @@
       <c r="A36">
         <v>32</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="6">
         <v>18</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="6">
         <v>57.4</v>
       </c>
     </row>
@@ -1290,10 +1418,10 @@
       <c r="A37">
         <v>33</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="6">
         <v>15.9</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="6">
         <v>7.8</v>
       </c>
     </row>
@@ -1301,10 +1429,10 @@
       <c r="A38">
         <v>34</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="6">
         <v>44.1</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="6">
         <v>13</v>
       </c>
     </row>
@@ -1312,10 +1440,10 @@
       <c r="A39">
         <v>35</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="6">
         <v>101.6</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="6">
         <v>1418.3</v>
       </c>
     </row>
@@ -1323,10 +1451,10 @@
       <c r="A40">
         <v>36</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="6">
         <v>38.700000000000003</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="6">
         <v>16</v>
       </c>
     </row>
@@ -1334,10 +1462,10 @@
       <c r="A41">
         <v>37</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="6">
         <v>78.599999999999994</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="6">
         <v>39.1</v>
       </c>
     </row>
@@ -1345,10 +1473,10 @@
       <c r="A42">
         <v>38</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="6">
         <v>52.9</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="6">
         <v>232</v>
       </c>
     </row>
@@ -1356,10 +1484,10 @@
       <c r="A43">
         <v>39</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="6">
         <v>184.4</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="6">
         <v>3.8</v>
       </c>
     </row>
@@ -1367,10 +1495,10 @@
       <c r="A44">
         <v>40</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="6">
         <v>71.599999999999994</v>
       </c>
     </row>
@@ -1378,7 +1506,7 @@
       <c r="A45">
         <v>41</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="6">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -1386,7 +1514,7 @@
       <c r="A46">
         <v>42</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="6">
         <v>30.9</v>
       </c>
     </row>
@@ -1394,7 +1522,7 @@
       <c r="A47">
         <v>43</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="6">
         <v>74.099999999999994</v>
       </c>
     </row>
@@ -1402,7 +1530,7 @@
       <c r="A48">
         <v>44</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="6">
         <v>24.7</v>
       </c>
     </row>
@@ -1410,7 +1538,7 @@
       <c r="A49">
         <v>45</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="6">
         <v>59.4</v>
       </c>
     </row>
@@ -1418,7 +1546,7 @@
       <c r="A50">
         <v>46</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="6">
         <v>11.1</v>
       </c>
     </row>
@@ -1426,7 +1554,7 @@
       <c r="A51">
         <v>47</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="6">
         <v>10.1</v>
       </c>
     </row>
@@ -1434,7 +1562,7 @@
       <c r="A52">
         <v>48</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="6">
         <v>17.899999999999999</v>
       </c>
     </row>
@@ -1442,7 +1570,7 @@
       <c r="A53">
         <v>49</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="6">
         <v>91.9</v>
       </c>
     </row>
@@ -1450,7 +1578,7 @@
       <c r="A54">
         <v>50</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="6">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -1458,7 +1586,7 @@
       <c r="A55">
         <v>51</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="6">
         <v>18</v>
       </c>
     </row>
@@ -1466,7 +1594,7 @@
       <c r="A56">
         <v>52</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="6">
         <v>46</v>
       </c>
     </row>
@@ -1474,7 +1602,7 @@
       <c r="A57">
         <v>53</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="6">
         <v>19.3</v>
       </c>
     </row>
@@ -1482,7 +1610,7 @@
       <c r="A58">
         <v>54</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="6">
         <v>38.799999999999997</v>
       </c>
     </row>
@@ -1490,7 +1618,7 @@
       <c r="A59">
         <v>55</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="6">
         <v>11.8</v>
       </c>
     </row>
@@ -1498,7 +1626,7 @@
       <c r="A60">
         <v>56</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="6">
         <v>36.200000000000003</v>
       </c>
     </row>
@@ -1506,7 +1634,7 @@
       <c r="A61">
         <v>57</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="6">
         <v>17.5</v>
       </c>
     </row>
@@ -1514,7 +1642,7 @@
       <c r="A62">
         <v>58</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="6">
         <v>36.299999999999997</v>
       </c>
     </row>
@@ -1522,7 +1650,7 @@
       <c r="A63">
         <v>59</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="6">
         <v>19.2</v>
       </c>
     </row>
@@ -1530,7 +1658,7 @@
       <c r="A64">
         <v>60</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="6">
         <v>16</v>
       </c>
     </row>
@@ -1538,7 +1666,7 @@
       <c r="A65">
         <v>61</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="6">
         <v>42.8</v>
       </c>
     </row>
@@ -1546,7 +1674,7 @@
       <c r="A66">
         <v>62</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="6">
         <v>26.7</v>
       </c>
     </row>
@@ -1554,7 +1682,7 @@
       <c r="A67">
         <v>63</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="6">
         <v>38.9</v>
       </c>
     </row>
@@ -1562,7 +1690,7 @@
       <c r="A68">
         <v>64</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="6">
         <v>24.5</v>
       </c>
     </row>
@@ -1570,7 +1698,7 @@
       <c r="A69">
         <v>65</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="6">
         <v>72.400000000000006</v>
       </c>
     </row>
@@ -1578,7 +1706,7 @@
       <c r="A70">
         <v>66</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="6">
         <v>16.100000000000001</v>
       </c>
     </row>
@@ -1586,7 +1714,7 @@
       <c r="A71">
         <v>67</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="6">
         <v>85.2</v>
       </c>
     </row>
@@ -1594,7 +1722,7 @@
       <c r="A72">
         <v>68</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="6">
         <v>153.9</v>
       </c>
     </row>
@@ -1602,7 +1730,7 @@
       <c r="A73">
         <v>69</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="6">
         <v>28.7</v>
       </c>
     </row>
@@ -1610,7 +1738,7 @@
       <c r="A74">
         <v>70</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="6">
         <v>237.5</v>
       </c>
     </row>
@@ -1618,7 +1746,7 @@
       <c r="A75">
         <v>71</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="6">
         <v>320.10000000000002</v>
       </c>
     </row>
@@ -1626,7 +1754,7 @@
       <c r="A76">
         <v>72</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="6">
         <v>60.5</v>
       </c>
     </row>
@@ -1634,7 +1762,7 @@
       <c r="A77">
         <v>73</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="6">
         <v>9.1</v>
       </c>
     </row>
@@ -1642,7 +1770,7 @@
       <c r="A78">
         <v>74</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="6">
         <v>7</v>
       </c>
     </row>
@@ -1650,7 +1778,7 @@
       <c r="A79">
         <v>75</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="6">
         <v>31.6</v>
       </c>
     </row>
@@ -1658,7 +1786,7 @@
       <c r="A80">
         <v>76</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="6">
         <v>245.3</v>
       </c>
     </row>
@@ -1666,7 +1794,7 @@
       <c r="A81">
         <v>77</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="6">
         <v>69.5</v>
       </c>
     </row>
@@ -1674,7 +1802,7 @@
       <c r="A82">
         <v>78</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="6">
         <v>84.2</v>
       </c>
     </row>
@@ -1682,7 +1810,7 @@
       <c r="A83">
         <v>79</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="6">
         <v>29.2</v>
       </c>
     </row>
@@ -1690,7 +1818,7 @@
       <c r="A84">
         <v>80</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="6">
         <v>17.399999999999999</v>
       </c>
     </row>
@@ -1698,7 +1826,7 @@
       <c r="A85">
         <v>81</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="6">
         <v>56.2</v>
       </c>
     </row>
@@ -1706,7 +1834,7 @@
       <c r="A86">
         <v>82</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="6">
         <v>11.9</v>
       </c>
     </row>
@@ -1714,7 +1842,7 @@
       <c r="A87">
         <v>83</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="6">
         <v>30.9</v>
       </c>
     </row>
@@ -1722,7 +1850,7 @@
       <c r="A88">
         <v>84</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="6">
         <v>65</v>
       </c>
     </row>
@@ -1730,7 +1858,7 @@
       <c r="A89">
         <v>85</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="6">
         <v>39.5</v>
       </c>
     </row>
@@ -1738,7 +1866,7 @@
       <c r="A90">
         <v>86</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="6">
         <v>65.900000000000006</v>
       </c>
     </row>
@@ -1746,7 +1874,7 @@
       <c r="A91">
         <v>87</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="6">
         <v>23.8</v>
       </c>
     </row>
@@ -1754,7 +1882,7 @@
       <c r="A92">
         <v>88</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="6">
         <v>71.2</v>
       </c>
     </row>
@@ -1762,7 +1890,7 @@
       <c r="A93">
         <v>89</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="6">
         <v>58.1</v>
       </c>
     </row>
@@ -1770,7 +1898,7 @@
       <c r="A94">
         <v>90</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="6">
         <v>6.7</v>
       </c>
     </row>
@@ -1778,7 +1906,7 @@
       <c r="A95">
         <v>91</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="6">
         <v>12.7</v>
       </c>
     </row>
@@ -1786,7 +1914,7 @@
       <c r="A96">
         <v>92</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="6">
         <v>17.8</v>
       </c>
     </row>
@@ -1794,7 +1922,7 @@
       <c r="A97">
         <v>93</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="6">
         <v>75.599999999999994</v>
       </c>
     </row>
@@ -1802,7 +1930,7 @@
       <c r="A98">
         <v>94</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="6">
         <v>52.2</v>
       </c>
     </row>
@@ -1810,7 +1938,7 @@
       <c r="A99">
         <v>95</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="6">
         <v>51.1</v>
       </c>
     </row>
@@ -1818,7 +1946,7 @@
       <c r="A100">
         <v>96</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="6">
         <v>45.6</v>
       </c>
     </row>
@@ -1826,7 +1954,7 @@
       <c r="A101">
         <v>97</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="6">
         <v>74.099999999999994</v>
       </c>
     </row>
@@ -1834,7 +1962,7 @@
       <c r="A102">
         <v>98</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="6">
         <v>102.5</v>
       </c>
     </row>
@@ -1842,7 +1970,7 @@
       <c r="A103">
         <v>99</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="6">
         <v>21.2</v>
       </c>
     </row>
@@ -1850,7 +1978,7 @@
       <c r="A104">
         <v>100</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="6">
         <v>7.2</v>
       </c>
     </row>
@@ -1858,7 +1986,7 @@
       <c r="A105">
         <v>101</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="6">
         <v>76.599999999999994</v>
       </c>
     </row>
@@ -1866,7 +1994,7 @@
       <c r="A106">
         <v>102</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="6">
         <v>30.5</v>
       </c>
     </row>
@@ -1874,7 +2002,7 @@
       <c r="A107">
         <v>103</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="6">
         <v>40</v>
       </c>
     </row>
@@ -1882,7 +2010,7 @@
       <c r="A108">
         <v>104</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="6">
         <v>31.7</v>
       </c>
     </row>
@@ -1890,7 +2018,7 @@
       <c r="A109">
         <v>105</v>
       </c>
-      <c r="B109" s="9">
+      <c r="B109" s="6">
         <v>11.8</v>
       </c>
     </row>
@@ -1898,7 +2026,7 @@
       <c r="A110">
         <v>106</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="6">
         <v>7.8</v>
       </c>
     </row>
@@ -1906,7 +2034,7 @@
       <c r="A111">
         <v>107</v>
       </c>
-      <c r="B111" s="9">
+      <c r="B111" s="6">
         <v>104.6</v>
       </c>
     </row>
@@ -1914,7 +2042,7 @@
       <c r="A112">
         <v>108</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="6">
         <v>119.7</v>
       </c>
     </row>
@@ -1922,7 +2050,7 @@
       <c r="A113">
         <v>109</v>
       </c>
-      <c r="B113" s="9">
+      <c r="B113" s="6">
         <v>101</v>
       </c>
     </row>
@@ -1930,7 +2058,7 @@
       <c r="A114">
         <v>110</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="6">
         <v>47.3</v>
       </c>
     </row>
@@ -1938,7 +2066,7 @@
       <c r="A115">
         <v>111</v>
       </c>
-      <c r="B115" s="9">
+      <c r="B115" s="6">
         <v>50.4</v>
       </c>
     </row>
@@ -1946,7 +2074,7 @@
       <c r="A116">
         <v>112</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="6">
         <v>24.5</v>
       </c>
     </row>
@@ -1954,7 +2082,7 @@
       <c r="A117">
         <v>113</v>
       </c>
-      <c r="B117" s="9">
+      <c r="B117" s="6">
         <v>40.799999999999997</v>
       </c>
     </row>
@@ -1962,7 +2090,7 @@
       <c r="A118">
         <v>114</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="6">
         <v>24.9</v>
       </c>
     </row>
@@ -1970,7 +2098,7 @@
       <c r="A119">
         <v>115</v>
       </c>
-      <c r="B119" s="9">
+      <c r="B119" s="6">
         <v>21.5</v>
       </c>
     </row>
@@ -1978,7 +2106,7 @@
       <c r="A120">
         <v>116</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="6">
         <v>47.1</v>
       </c>
     </row>
@@ -1986,7 +2114,7 @@
       <c r="A121">
         <v>117</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="6">
         <v>226</v>
       </c>
     </row>
@@ -1994,7 +2122,7 @@
       <c r="A122">
         <v>118</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="6">
         <v>5.3</v>
       </c>
     </row>
@@ -2002,7 +2130,7 @@
       <c r="A123">
         <v>119</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="6">
         <v>71.5</v>
       </c>
     </row>
@@ -2010,7 +2138,7 @@
       <c r="A124">
         <v>120</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="6">
         <v>77.2</v>
       </c>
     </row>
@@ -2018,7 +2146,7 @@
       <c r="A125">
         <v>121</v>
       </c>
-      <c r="B125" s="9">
+      <c r="B125" s="6">
         <v>10.6</v>
       </c>
     </row>
@@ -2026,7 +2154,7 @@
       <c r="A126">
         <v>122</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="6">
         <v>52.8</v>
       </c>
     </row>
@@ -2034,7 +2162,7 @@
       <c r="A127">
         <v>123</v>
       </c>
-      <c r="B127" s="9">
+      <c r="B127" s="6">
         <v>42.3</v>
       </c>
     </row>
@@ -2042,7 +2170,7 @@
       <c r="A128">
         <v>124</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="6">
         <v>23.3</v>
       </c>
     </row>
@@ -2050,7 +2178,7 @@
       <c r="A129">
         <v>125</v>
       </c>
-      <c r="B129" s="9">
+      <c r="B129" s="6">
         <v>22.6</v>
       </c>
     </row>
@@ -2058,7 +2186,7 @@
       <c r="A130">
         <v>126</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="6">
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -2066,7 +2194,7 @@
       <c r="A131">
         <v>127</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="6">
         <v>228.2</v>
       </c>
     </row>
@@ -2074,7 +2202,7 @@
       <c r="A132">
         <v>128</v>
       </c>
-      <c r="B132" s="9">
+      <c r="B132" s="6">
         <v>447</v>
       </c>
     </row>
@@ -2082,7 +2210,7 @@
       <c r="A133">
         <v>129</v>
       </c>
-      <c r="B133" s="9">
+      <c r="B133" s="6">
         <v>201</v>
       </c>
     </row>
@@ -2090,7 +2218,7 @@
       <c r="A134">
         <v>130</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="6">
         <v>28.1</v>
       </c>
     </row>
@@ -2098,7 +2226,7 @@
       <c r="A135">
         <v>131</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="6">
         <v>51.3</v>
       </c>
     </row>
@@ -2106,7 +2234,7 @@
       <c r="A136">
         <v>132</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="6">
         <v>56.5</v>
       </c>
     </row>
@@ -2114,7 +2242,7 @@
       <c r="A137">
         <v>133</v>
       </c>
-      <c r="B137" s="9">
+      <c r="B137" s="6">
         <v>16.2</v>
       </c>
     </row>
@@ -2122,7 +2250,7 @@
       <c r="A138">
         <v>134</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="6">
         <v>29</v>
       </c>
     </row>
@@ -2130,7 +2258,7 @@
       <c r="A139">
         <v>135</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B139" s="6">
         <v>66.5</v>
       </c>
     </row>
@@ -2138,7 +2266,7 @@
       <c r="A140">
         <v>136</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="6">
         <v>24.4</v>
       </c>
     </row>
@@ -2146,7 +2274,7 @@
       <c r="A141">
         <v>137</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="6">
         <v>6</v>
       </c>
     </row>
@@ -2154,7 +2282,7 @@
       <c r="A142">
         <v>138</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="6">
         <v>10</v>
       </c>
     </row>
@@ -2162,7 +2290,7 @@
       <c r="A143">
         <v>139</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="6">
         <v>49.7</v>
       </c>
     </row>
@@ -2170,7 +2298,7 @@
       <c r="A144">
         <v>140</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="6">
         <v>26.7</v>
       </c>
     </row>
@@ -2178,7 +2306,7 @@
       <c r="A145">
         <v>141</v>
       </c>
-      <c r="B145" s="9">
+      <c r="B145" s="6">
         <v>27.8</v>
       </c>
     </row>
@@ -2186,7 +2314,7 @@
       <c r="A146">
         <v>142</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="6">
         <v>157.80000000000001</v>
       </c>
     </row>
@@ -2194,7 +2322,7 @@
       <c r="A147">
         <v>143</v>
       </c>
-      <c r="B147" s="9">
+      <c r="B147" s="6">
         <v>41.5</v>
       </c>
     </row>
@@ -2202,7 +2330,7 @@
       <c r="A148">
         <v>144</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="6">
         <v>17.899999999999999</v>
       </c>
     </row>
@@ -2210,7 +2338,7 @@
       <c r="A149">
         <v>145</v>
       </c>
-      <c r="B149" s="9">
+      <c r="B149" s="6">
         <v>35.5</v>
       </c>
     </row>
@@ -2218,7 +2346,7 @@
       <c r="A150">
         <v>146</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="6">
         <v>366.3</v>
       </c>
     </row>
@@ -2226,7 +2354,7 @@
       <c r="A151">
         <v>147</v>
       </c>
-      <c r="B151" s="9">
+      <c r="B151" s="6">
         <v>11.6</v>
       </c>
     </row>
@@ -2234,7 +2362,7 @@
       <c r="A152">
         <v>148</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="6">
         <v>248.1</v>
       </c>
     </row>
@@ -2242,7 +2370,7 @@
       <c r="A153">
         <v>149</v>
       </c>
-      <c r="B153" s="9">
+      <c r="B153" s="6">
         <v>172.6</v>
       </c>
     </row>
@@ -2250,7 +2378,7 @@
       <c r="A154">
         <v>150</v>
       </c>
-      <c r="B154" s="9">
+      <c r="B154" s="6">
         <v>32.1</v>
       </c>
     </row>
@@ -2258,7 +2386,7 @@
       <c r="A155">
         <v>151</v>
       </c>
-      <c r="B155" s="9">
+      <c r="B155" s="6">
         <v>26.7</v>
       </c>
     </row>
@@ -2266,7 +2394,7 @@
       <c r="A156">
         <v>152</v>
       </c>
-      <c r="B156" s="9">
+      <c r="B156" s="6">
         <v>168.6</v>
       </c>
     </row>
@@ -2274,7 +2402,7 @@
       <c r="A157">
         <v>153</v>
       </c>
-      <c r="B157" s="9">
+      <c r="B157" s="6">
         <v>49.1</v>
       </c>
     </row>
@@ -2282,7 +2410,7 @@
       <c r="A158">
         <v>154</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="6">
         <v>21.8</v>
       </c>
     </row>
@@ -2290,7 +2418,7 @@
       <c r="A159">
         <v>155</v>
       </c>
-      <c r="B159" s="9">
+      <c r="B159" s="6">
         <v>257.60000000000002</v>
       </c>
     </row>
@@ -2298,7 +2426,7 @@
       <c r="A160">
         <v>156</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="6">
         <v>45.6</v>
       </c>
     </row>
@@ -2306,7 +2434,7 @@
       <c r="A161">
         <v>157</v>
       </c>
-      <c r="B161" s="9">
+      <c r="B161" s="6">
         <v>53.9</v>
       </c>
     </row>
@@ -2314,7 +2442,7 @@
       <c r="A162">
         <v>158</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="6">
         <v>39.6</v>
       </c>
     </row>
@@ -2322,7 +2450,7 @@
       <c r="A163">
         <v>159</v>
       </c>
-      <c r="B163" s="9">
+      <c r="B163" s="6">
         <v>27.7</v>
       </c>
     </row>
@@ -2330,7 +2458,7 @@
       <c r="A164">
         <v>160</v>
       </c>
-      <c r="B164" s="9">
+      <c r="B164" s="6">
         <v>43.3</v>
       </c>
     </row>
@@ -2338,7 +2466,7 @@
       <c r="A165">
         <v>161</v>
       </c>
-      <c r="B165" s="9">
+      <c r="B165" s="6">
         <v>25.8</v>
       </c>
     </row>
@@ -2346,7 +2474,7 @@
       <c r="A166">
         <v>162</v>
       </c>
-      <c r="B166" s="9">
+      <c r="B166" s="6">
         <v>64.7</v>
       </c>
     </row>
@@ -2354,7 +2482,7 @@
       <c r="A167">
         <v>163</v>
       </c>
-      <c r="B167" s="9">
+      <c r="B167" s="6">
         <v>115.1</v>
       </c>
     </row>
@@ -2362,7 +2490,7 @@
       <c r="A168">
         <v>164</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="6">
         <v>118.8</v>
       </c>
     </row>
@@ -2370,7 +2498,7 @@
       <c r="A169">
         <v>165</v>
       </c>
-      <c r="B169" s="9">
+      <c r="B169" s="6">
         <v>132.80000000000001</v>
       </c>
     </row>
@@ -2378,7 +2506,7 @@
       <c r="A170">
         <v>166</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="6">
         <v>182.7</v>
       </c>
     </row>
@@ -2386,7 +2514,7 @@
       <c r="A171">
         <v>167</v>
       </c>
-      <c r="B171" s="9">
+      <c r="B171" s="6">
         <v>84.5</v>
       </c>
     </row>
@@ -2394,7 +2522,7 @@
       <c r="A172">
         <v>168</v>
       </c>
-      <c r="B172" s="9">
+      <c r="B172" s="6">
         <v>20.100000000000001</v>
       </c>
     </row>
@@ -2402,7 +2530,7 @@
       <c r="A173">
         <v>169</v>
       </c>
-      <c r="B173" s="9">
+      <c r="B173" s="6">
         <v>104.4</v>
       </c>
     </row>
@@ -2410,7 +2538,7 @@
       <c r="A174">
         <v>170</v>
       </c>
-      <c r="B174" s="9">
+      <c r="B174" s="6">
         <v>6.7</v>
       </c>
     </row>
@@ -2418,7 +2546,7 @@
       <c r="A175">
         <v>171</v>
       </c>
-      <c r="B175" s="9">
+      <c r="B175" s="6">
         <v>18</v>
       </c>
     </row>
@@ -2426,7 +2554,7 @@
       <c r="A176">
         <v>172</v>
       </c>
-      <c r="B176" s="9">
+      <c r="B176" s="6">
         <v>51.5</v>
       </c>
     </row>
@@ -2434,7 +2562,7 @@
       <c r="A177">
         <v>173</v>
       </c>
-      <c r="B177" s="9">
+      <c r="B177" s="6">
         <v>6.5</v>
       </c>
     </row>
@@ -2442,7 +2570,7 @@
       <c r="A178">
         <v>174</v>
       </c>
-      <c r="B178" s="9">
+      <c r="B178" s="6">
         <v>178.2</v>
       </c>
     </row>
@@ -2450,7 +2578,7 @@
       <c r="A179">
         <v>175</v>
       </c>
-      <c r="B179" s="9">
+      <c r="B179" s="6">
         <v>13.1</v>
       </c>
     </row>
@@ -2458,7 +2586,7 @@
       <c r="A180">
         <v>176</v>
       </c>
-      <c r="B180" s="9">
+      <c r="B180" s="6">
         <v>7.9</v>
       </c>
     </row>
@@ -2466,7 +2594,7 @@
       <c r="A181">
         <v>177</v>
       </c>
-      <c r="B181" s="9">
+      <c r="B181" s="6">
         <v>17.100000000000001</v>
       </c>
     </row>
@@ -2474,7 +2602,7 @@
       <c r="A182">
         <v>178</v>
       </c>
-      <c r="B182" s="9">
+      <c r="B182" s="6">
         <v>17</v>
       </c>
     </row>
@@ -2482,7 +2610,7 @@
       <c r="A183">
         <v>179</v>
       </c>
-      <c r="B183" s="9">
+      <c r="B183" s="6">
         <v>37</v>
       </c>
     </row>
@@ -2490,7 +2618,7 @@
       <c r="A184">
         <v>180</v>
       </c>
-      <c r="B184" s="9">
+      <c r="B184" s="6">
         <v>32.200000000000003</v>
       </c>
     </row>
@@ -2498,7 +2626,7 @@
       <c r="A185">
         <v>181</v>
       </c>
-      <c r="B185" s="9">
+      <c r="B185" s="6">
         <v>112.2</v>
       </c>
     </row>
@@ -2506,7 +2634,7 @@
       <c r="A186">
         <v>182</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="6">
         <v>31.9</v>
       </c>
     </row>
@@ -2514,7 +2642,7 @@
       <c r="A187">
         <v>183</v>
       </c>
-      <c r="B187" s="9">
+      <c r="B187" s="6">
         <v>45.7</v>
       </c>
     </row>
@@ -2522,7 +2650,7 @@
       <c r="A188">
         <v>184</v>
       </c>
-      <c r="B188" s="9">
+      <c r="B188" s="6">
         <v>13.4</v>
       </c>
     </row>
@@ -2530,7 +2658,7 @@
       <c r="A189">
         <v>185</v>
       </c>
-      <c r="B189" s="9">
+      <c r="B189" s="6">
         <v>64.099999999999994</v>
       </c>
     </row>
@@ -2538,7 +2666,7 @@
       <c r="A190">
         <v>186</v>
       </c>
-      <c r="B190" s="9">
+      <c r="B190" s="6">
         <v>16.8</v>
       </c>
     </row>
@@ -2546,7 +2674,7 @@
       <c r="A191">
         <v>187</v>
       </c>
-      <c r="B191" s="9">
+      <c r="B191" s="6">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -2554,7 +2682,7 @@
       <c r="A192">
         <v>188</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="6">
         <v>149.4</v>
       </c>
     </row>
@@ -2562,7 +2690,7 @@
       <c r="A193">
         <v>189</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B193" s="6">
         <v>12.5</v>
       </c>
     </row>
@@ -2570,7 +2698,7 @@
       <c r="A194">
         <v>190</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="6">
         <v>12.1</v>
       </c>
     </row>
@@ -2578,7 +2706,7 @@
       <c r="A195">
         <v>191</v>
       </c>
-      <c r="B195" s="9">
+      <c r="B195" s="6">
         <v>15.1</v>
       </c>
     </row>
@@ -2586,7 +2714,7 @@
       <c r="A196">
         <v>192</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B196" s="6">
         <v>75.3</v>
       </c>
     </row>
@@ -2594,7 +2722,7 @@
       <c r="A197">
         <v>193</v>
       </c>
-      <c r="B197" s="9">
+      <c r="B197" s="6">
         <v>7.7</v>
       </c>
     </row>
@@ -2602,7 +2730,7 @@
       <c r="A198">
         <v>194</v>
       </c>
-      <c r="B198" s="9">
+      <c r="B198" s="6">
         <v>25</v>
       </c>
     </row>
@@ -2610,7 +2738,7 @@
       <c r="A199">
         <v>195</v>
       </c>
-      <c r="B199" s="9">
+      <c r="B199" s="6">
         <v>69.599999999999994</v>
       </c>
     </row>
@@ -2618,7 +2746,7 @@
       <c r="A200">
         <v>196</v>
       </c>
-      <c r="B200" s="9">
+      <c r="B200" s="6">
         <v>278.5</v>
       </c>
     </row>
@@ -2626,7 +2754,7 @@
       <c r="A201">
         <v>197</v>
       </c>
-      <c r="B201" s="9">
+      <c r="B201" s="6">
         <v>28</v>
       </c>
     </row>
@@ -2634,7 +2762,7 @@
       <c r="A202">
         <v>198</v>
       </c>
-      <c r="B202" s="9">
+      <c r="B202" s="6">
         <v>40.299999999999997</v>
       </c>
     </row>
@@ -2642,7 +2770,7 @@
       <c r="A203">
         <v>199</v>
       </c>
-      <c r="B203" s="9">
+      <c r="B203" s="6">
         <v>15.3</v>
       </c>
     </row>
@@ -2650,7 +2778,7 @@
       <c r="A204">
         <v>200</v>
       </c>
-      <c r="B204" s="9">
+      <c r="B204" s="6">
         <v>304.3</v>
       </c>
     </row>
@@ -2658,7 +2786,7 @@
       <c r="A205">
         <v>201</v>
       </c>
-      <c r="B205" s="9">
+      <c r="B205" s="6">
         <v>32.799999999999997</v>
       </c>
     </row>
@@ -2666,7 +2794,7 @@
       <c r="A206">
         <v>202</v>
       </c>
-      <c r="B206" s="9">
+      <c r="B206" s="6">
         <v>35.6</v>
       </c>
     </row>
@@ -2674,7 +2802,7 @@
       <c r="A207">
         <v>203</v>
       </c>
-      <c r="B207" s="9">
+      <c r="B207" s="6">
         <v>44.3</v>
       </c>
     </row>
@@ -2682,7 +2810,7 @@
       <c r="A208">
         <v>204</v>
       </c>
-      <c r="B208" s="9">
+      <c r="B208" s="6">
         <v>14.5</v>
       </c>
     </row>
@@ -2690,7 +2818,7 @@
       <c r="A209">
         <v>205</v>
       </c>
-      <c r="B209" s="9">
+      <c r="B209" s="6">
         <v>37.6</v>
       </c>
     </row>
@@ -2698,7 +2826,7 @@
       <c r="A210">
         <v>206</v>
       </c>
-      <c r="B210" s="9">
+      <c r="B210" s="6">
         <v>10.1</v>
       </c>
     </row>
@@ -2706,7 +2834,7 @@
       <c r="A211">
         <v>207</v>
       </c>
-      <c r="B211" s="9">
+      <c r="B211" s="6">
         <v>181.4</v>
       </c>
     </row>
@@ -2714,7 +2842,7 @@
       <c r="A212">
         <v>208</v>
       </c>
-      <c r="B212" s="9">
+      <c r="B212" s="6">
         <v>32.5</v>
       </c>
     </row>
@@ -2722,7 +2850,7 @@
       <c r="A213">
         <v>209</v>
       </c>
-      <c r="B213" s="9">
+      <c r="B213" s="6">
         <v>32</v>
       </c>
     </row>
@@ -2730,7 +2858,7 @@
       <c r="A214">
         <v>210</v>
       </c>
-      <c r="B214" s="9">
+      <c r="B214" s="6">
         <v>129.6</v>
       </c>
     </row>
@@ -2738,7 +2866,7 @@
       <c r="A215">
         <v>211</v>
       </c>
-      <c r="B215" s="9">
+      <c r="B215" s="6">
         <v>10.6</v>
       </c>
     </row>
@@ -2746,7 +2874,7 @@
       <c r="A216">
         <v>212</v>
       </c>
-      <c r="B216" s="9">
+      <c r="B216" s="6">
         <v>165.5</v>
       </c>
     </row>
@@ -2754,7 +2882,7 @@
       <c r="A217">
         <v>213</v>
       </c>
-      <c r="B217" s="9">
+      <c r="B217" s="6">
         <v>187.9</v>
       </c>
     </row>
@@ -2762,7 +2890,7 @@
       <c r="A218">
         <v>214</v>
       </c>
-      <c r="B218" s="9">
+      <c r="B218" s="6">
         <v>16.899999999999999</v>
       </c>
     </row>
@@ -2770,7 +2898,7 @@
       <c r="A219">
         <v>215</v>
       </c>
-      <c r="B219" s="9">
+      <c r="B219" s="6">
         <v>78.5</v>
       </c>
     </row>
@@ -2778,7 +2906,7 @@
       <c r="A220">
         <v>216</v>
       </c>
-      <c r="B220" s="9">
+      <c r="B220" s="6">
         <v>34.299999999999997</v>
       </c>
     </row>
@@ -2786,7 +2914,7 @@
       <c r="A221">
         <v>217</v>
       </c>
-      <c r="B221" s="9">
+      <c r="B221" s="6">
         <v>96</v>
       </c>
     </row>
@@ -2794,7 +2922,7 @@
       <c r="A222">
         <v>218</v>
       </c>
-      <c r="B222" s="9">
+      <c r="B222" s="6">
         <v>39.700000000000003</v>
       </c>
     </row>
@@ -2802,7 +2930,7 @@
       <c r="A223">
         <v>219</v>
       </c>
-      <c r="B223" s="9">
+      <c r="B223" s="6">
         <v>14.8</v>
       </c>
     </row>
@@ -2810,7 +2938,7 @@
       <c r="A224">
         <v>220</v>
       </c>
-      <c r="B224" s="9">
+      <c r="B224" s="6">
         <v>73.5</v>
       </c>
     </row>
@@ -2818,7 +2946,7 @@
       <c r="A225">
         <v>221</v>
       </c>
-      <c r="B225" s="9">
+      <c r="B225" s="6">
         <v>30.2</v>
       </c>
     </row>
@@ -2826,7 +2954,7 @@
       <c r="A226">
         <v>222</v>
       </c>
-      <c r="B226" s="9">
+      <c r="B226" s="6">
         <v>45.9</v>
       </c>
     </row>
@@ -2834,7 +2962,7 @@
       <c r="A227">
         <v>223</v>
       </c>
-      <c r="B227" s="9">
+      <c r="B227" s="6">
         <v>105.9</v>
       </c>
     </row>
@@ -2842,7 +2970,7 @@
       <c r="A228">
         <v>224</v>
       </c>
-      <c r="B228" s="9">
+      <c r="B228" s="6">
         <v>136.1</v>
       </c>
     </row>
@@ -2850,7 +2978,7 @@
       <c r="A229">
         <v>225</v>
       </c>
-      <c r="B229" s="9">
+      <c r="B229" s="6">
         <v>73.599999999999994</v>
       </c>
     </row>
@@ -2858,7 +2986,7 @@
       <c r="A230">
         <v>226</v>
       </c>
-      <c r="B230" s="9">
+      <c r="B230" s="6">
         <v>8.5</v>
       </c>
     </row>
@@ -2866,7 +2994,7 @@
       <c r="A231">
         <v>227</v>
       </c>
-      <c r="B231" s="9">
+      <c r="B231" s="6">
         <v>78.8</v>
       </c>
     </row>
@@ -2874,7 +3002,7 @@
       <c r="A232">
         <v>228</v>
       </c>
-      <c r="B232" s="9">
+      <c r="B232" s="6">
         <v>27.7</v>
       </c>
     </row>
@@ -2882,7 +3010,7 @@
       <c r="A233">
         <v>229</v>
       </c>
-      <c r="B233" s="9">
+      <c r="B233" s="6">
         <v>117.1</v>
       </c>
     </row>
@@ -2890,7 +3018,7 @@
       <c r="A234">
         <v>230</v>
       </c>
-      <c r="B234" s="9">
+      <c r="B234" s="6">
         <v>30.9</v>
       </c>
     </row>
@@ -2898,7 +3026,7 @@
       <c r="A235">
         <v>231</v>
       </c>
-      <c r="B235" s="9">
+      <c r="B235" s="6">
         <v>169.8</v>
       </c>
     </row>
@@ -2906,7 +3034,7 @@
       <c r="A236">
         <v>232</v>
       </c>
-      <c r="B236" s="9">
+      <c r="B236" s="6">
         <v>65.2</v>
       </c>
     </row>
@@ -2914,7 +3042,7 @@
       <c r="A237">
         <v>233</v>
       </c>
-      <c r="B237" s="9">
+      <c r="B237" s="6">
         <v>38</v>
       </c>
     </row>
@@ -2922,7 +3050,7 @@
       <c r="A238">
         <v>234</v>
       </c>
-      <c r="B238" s="9">
+      <c r="B238" s="6">
         <v>51.7</v>
       </c>
     </row>
@@ -2930,7 +3058,7 @@
       <c r="A239">
         <v>235</v>
       </c>
-      <c r="B239" s="9">
+      <c r="B239" s="6">
         <v>6</v>
       </c>
     </row>
@@ -2938,7 +3066,7 @@
       <c r="A240">
         <v>236</v>
       </c>
-      <c r="B240" s="9">
+      <c r="B240" s="6">
         <v>69.400000000000006</v>
       </c>
     </row>
@@ -2946,7 +3074,7 @@
       <c r="A241">
         <v>237</v>
       </c>
-      <c r="B241" s="9">
+      <c r="B241" s="6">
         <v>42.9</v>
       </c>
     </row>
@@ -2954,7 +3082,7 @@
       <c r="A242">
         <v>238</v>
       </c>
-      <c r="B242" s="9">
+      <c r="B242" s="6">
         <v>12</v>
       </c>
     </row>
@@ -2962,7 +3090,7 @@
       <c r="A243">
         <v>239</v>
       </c>
-      <c r="B243" s="9">
+      <c r="B243" s="6">
         <v>58.3</v>
       </c>
     </row>
@@ -2970,7 +3098,7 @@
       <c r="A244">
         <v>240</v>
       </c>
-      <c r="B244" s="9">
+      <c r="B244" s="6">
         <v>53.1</v>
       </c>
     </row>
@@ -2978,7 +3106,7 @@
       <c r="A245">
         <v>241</v>
       </c>
-      <c r="B245" s="9">
+      <c r="B245" s="6">
         <v>55.3</v>
       </c>
     </row>
@@ -2986,7 +3114,7 @@
       <c r="A246">
         <v>242</v>
       </c>
-      <c r="B246" s="9">
+      <c r="B246" s="6">
         <v>33.700000000000003</v>
       </c>
     </row>
@@ -2994,7 +3122,7 @@
       <c r="A247">
         <v>243</v>
       </c>
-      <c r="B247" s="9">
+      <c r="B247" s="6">
         <v>87</v>
       </c>
     </row>
@@ -3002,7 +3130,7 @@
       <c r="A248">
         <v>244</v>
       </c>
-      <c r="B248" s="9">
+      <c r="B248" s="6">
         <v>88.2</v>
       </c>
     </row>
@@ -3010,7 +3138,7 @@
       <c r="A249">
         <v>245</v>
       </c>
-      <c r="B249" s="9">
+      <c r="B249" s="6">
         <v>41.9</v>
       </c>
     </row>
@@ -3018,7 +3146,7 @@
       <c r="A250">
         <v>246</v>
       </c>
-      <c r="B250" s="9">
+      <c r="B250" s="6">
         <v>35.6</v>
       </c>
     </row>
@@ -3026,7 +3154,7 @@
       <c r="A251">
         <v>247</v>
       </c>
-      <c r="B251" s="9">
+      <c r="B251" s="6">
         <v>23.6</v>
       </c>
     </row>
@@ -3034,7 +3162,7 @@
       <c r="A252">
         <v>248</v>
       </c>
-      <c r="B252" s="9">
+      <c r="B252" s="6">
         <v>20.3</v>
       </c>
     </row>
@@ -3042,7 +3170,7 @@
       <c r="A253">
         <v>249</v>
       </c>
-      <c r="B253" s="9">
+      <c r="B253" s="6">
         <v>72.2</v>
       </c>
     </row>
@@ -3050,7 +3178,7 @@
       <c r="A254">
         <v>250</v>
       </c>
-      <c r="B254" s="9">
+      <c r="B254" s="6">
         <v>21.4</v>
       </c>
     </row>
@@ -3058,7 +3186,7 @@
       <c r="A255">
         <v>251</v>
       </c>
-      <c r="B255" s="9">
+      <c r="B255" s="6">
         <v>8.6</v>
       </c>
     </row>
@@ -3066,7 +3194,7 @@
       <c r="A256">
         <v>252</v>
       </c>
-      <c r="B256" s="9">
+      <c r="B256" s="6">
         <v>49.2</v>
       </c>
     </row>
@@ -3074,7 +3202,7 @@
       <c r="A257">
         <v>253</v>
       </c>
-      <c r="B257" s="9">
+      <c r="B257" s="6">
         <v>121.6</v>
       </c>
     </row>
@@ -3082,7 +3210,7 @@
       <c r="A258">
         <v>254</v>
       </c>
-      <c r="B258" s="9">
+      <c r="B258" s="6">
         <v>28.5</v>
       </c>
     </row>
@@ -3090,7 +3218,7 @@
       <c r="A259">
         <v>255</v>
       </c>
-      <c r="B259" s="9">
+      <c r="B259" s="6">
         <v>94.6</v>
       </c>
     </row>
@@ -3098,7 +3226,7 @@
       <c r="A260">
         <v>256</v>
       </c>
-      <c r="B260" s="9">
+      <c r="B260" s="6">
         <v>63</v>
       </c>
     </row>
@@ -3106,7 +3234,7 @@
       <c r="A261">
         <v>257</v>
       </c>
-      <c r="B261" s="9">
+      <c r="B261" s="6">
         <v>13.2</v>
       </c>
     </row>
@@ -3114,7 +3242,7 @@
       <c r="A262">
         <v>258</v>
       </c>
-      <c r="B262" s="9">
+      <c r="B262" s="6">
         <v>53.3</v>
       </c>
     </row>
@@ -3122,7 +3250,7 @@
       <c r="A263">
         <v>259</v>
       </c>
-      <c r="B263" s="9">
+      <c r="B263" s="6">
         <v>33.9</v>
       </c>
     </row>
@@ -3130,7 +3258,7 @@
       <c r="A264">
         <v>260</v>
       </c>
-      <c r="B264" s="9">
+      <c r="B264" s="6">
         <v>77.8</v>
       </c>
     </row>
@@ -3138,7 +3266,7 @@
       <c r="A265">
         <v>261</v>
       </c>
-      <c r="B265" s="9">
+      <c r="B265" s="6">
         <v>2</v>
       </c>
     </row>
@@ -3146,7 +3274,7 @@
       <c r="A266">
         <v>262</v>
       </c>
-      <c r="B266" s="9">
+      <c r="B266" s="6">
         <v>91</v>
       </c>
     </row>
@@ -3154,7 +3282,7 @@
       <c r="A267">
         <v>263</v>
       </c>
-      <c r="B267" s="9">
+      <c r="B267" s="6">
         <v>82.8</v>
       </c>
     </row>
@@ -3162,7 +3290,7 @@
       <c r="A268">
         <v>264</v>
       </c>
-      <c r="B268" s="9">
+      <c r="B268" s="6">
         <v>14.4</v>
       </c>
     </row>
@@ -3170,7 +3298,7 @@
       <c r="A269">
         <v>265</v>
       </c>
-      <c r="B269" s="9">
+      <c r="B269" s="6">
         <v>116.8</v>
       </c>
     </row>
@@ -3178,7 +3306,7 @@
       <c r="A270">
         <v>266</v>
       </c>
-      <c r="B270" s="9">
+      <c r="B270" s="6">
         <v>32.4</v>
       </c>
     </row>
@@ -3186,7 +3314,7 @@
       <c r="A271">
         <v>267</v>
       </c>
-      <c r="B271" s="9">
+      <c r="B271" s="6">
         <v>46.1</v>
       </c>
     </row>
@@ -3194,7 +3322,7 @@
       <c r="A272">
         <v>268</v>
       </c>
-      <c r="B272" s="9">
+      <c r="B272" s="6">
         <v>94.4</v>
       </c>
     </row>
@@ -3202,7 +3330,7 @@
       <c r="A273">
         <v>269</v>
       </c>
-      <c r="B273" s="9">
+      <c r="B273" s="6">
         <v>156.19999999999999</v>
       </c>
     </row>
@@ -3210,7 +3338,7 @@
       <c r="A274">
         <v>270</v>
       </c>
-      <c r="B274" s="9">
+      <c r="B274" s="6">
         <v>45.6</v>
       </c>
     </row>
@@ -3218,7 +3346,7 @@
       <c r="A275">
         <v>271</v>
       </c>
-      <c r="B275" s="9">
+      <c r="B275" s="6">
         <v>78.3</v>
       </c>
     </row>
@@ -3226,7 +3354,7 @@
       <c r="A276">
         <v>272</v>
       </c>
-      <c r="B276" s="9">
+      <c r="B276" s="6">
         <v>60.7</v>
       </c>
     </row>
@@ -3234,7 +3362,7 @@
       <c r="A277">
         <v>273</v>
       </c>
-      <c r="B277" s="9">
+      <c r="B277" s="6">
         <v>17.8</v>
       </c>
     </row>
@@ -3242,7 +3370,7 @@
       <c r="A278">
         <v>274</v>
       </c>
-      <c r="B278" s="9">
+      <c r="B278" s="6">
         <v>213.7</v>
       </c>
     </row>
@@ -3250,7 +3378,7 @@
       <c r="A279">
         <v>275</v>
       </c>
-      <c r="B279" s="9">
+      <c r="B279" s="6">
         <v>86.3</v>
       </c>
     </row>
@@ -3258,7 +3386,7 @@
       <c r="A280">
         <v>276</v>
       </c>
-      <c r="B280" s="9">
+      <c r="B280" s="6">
         <v>44.8</v>
       </c>
     </row>
@@ -3266,7 +3394,7 @@
       <c r="A281">
         <v>277</v>
       </c>
-      <c r="B281" s="9">
+      <c r="B281" s="6">
         <v>118.6</v>
       </c>
     </row>
@@ -3274,7 +3402,7 @@
       <c r="A282">
         <v>278</v>
       </c>
-      <c r="B282" s="9">
+      <c r="B282" s="6">
         <v>68</v>
       </c>
     </row>
@@ -3282,7 +3410,7 @@
       <c r="A283">
         <v>279</v>
       </c>
-      <c r="B283" s="9">
+      <c r="B283" s="6">
         <v>21.5</v>
       </c>
     </row>
@@ -3290,7 +3418,7 @@
       <c r="A284">
         <v>280</v>
       </c>
-      <c r="B284" s="9">
+      <c r="B284" s="6">
         <v>110.5</v>
       </c>
     </row>
@@ -3298,7 +3426,7 @@
       <c r="A285">
         <v>281</v>
       </c>
-      <c r="B285" s="9">
+      <c r="B285" s="6">
         <v>41.3</v>
       </c>
     </row>
@@ -3306,7 +3434,7 @@
       <c r="A286">
         <v>282</v>
       </c>
-      <c r="B286" s="9">
+      <c r="B286" s="6">
         <v>74.099999999999994</v>
       </c>
     </row>
@@ -3314,7 +3442,7 @@
       <c r="A287">
         <v>283</v>
       </c>
-      <c r="B287" s="9">
+      <c r="B287" s="6">
         <v>105.5</v>
       </c>
     </row>
@@ -3322,7 +3450,7 @@
       <c r="A288">
         <v>284</v>
       </c>
-      <c r="B288" s="9">
+      <c r="B288" s="6">
         <v>104.7</v>
       </c>
     </row>
@@ -3330,7 +3458,7 @@
       <c r="A289">
         <v>285</v>
       </c>
-      <c r="B289" s="9">
+      <c r="B289" s="6">
         <v>279.10000000000002</v>
       </c>
     </row>
@@ -3338,7 +3466,7 @@
       <c r="A290">
         <v>286</v>
       </c>
-      <c r="B290" s="9">
+      <c r="B290" s="6">
         <v>47.8</v>
       </c>
     </row>
@@ -3346,7 +3474,7 @@
       <c r="A291">
         <v>287</v>
       </c>
-      <c r="B291" s="9">
+      <c r="B291" s="6">
         <v>32.6</v>
       </c>
     </row>
@@ -3354,7 +3482,7 @@
       <c r="A292">
         <v>288</v>
       </c>
-      <c r="B292" s="9">
+      <c r="B292" s="6">
         <v>18.2</v>
       </c>
     </row>
@@ -3362,7 +3490,7 @@
       <c r="A293">
         <v>289</v>
       </c>
-      <c r="B293" s="9">
+      <c r="B293" s="6">
         <v>20.2</v>
       </c>
     </row>
@@ -3370,7 +3498,7 @@
       <c r="A294">
         <v>290</v>
       </c>
-      <c r="B294" s="9">
+      <c r="B294" s="6">
         <v>78.7</v>
       </c>
     </row>
@@ -3378,7 +3506,7 @@
       <c r="A295">
         <v>291</v>
       </c>
-      <c r="B295" s="9">
+      <c r="B295" s="6">
         <v>61</v>
       </c>
     </row>
@@ -3386,7 +3514,7 @@
       <c r="A296">
         <v>292</v>
       </c>
-      <c r="B296" s="9">
+      <c r="B296" s="6">
         <v>15.8</v>
       </c>
     </row>
@@ -3394,7 +3522,7 @@
       <c r="A297">
         <v>293</v>
       </c>
-      <c r="B297" s="9">
+      <c r="B297" s="6">
         <v>20.6</v>
       </c>
     </row>
@@ -3402,7 +3530,7 @@
       <c r="A298">
         <v>294</v>
       </c>
-      <c r="B298" s="9">
+      <c r="B298" s="6">
         <v>24.7</v>
       </c>
     </row>
@@ -3410,7 +3538,7 @@
       <c r="A299">
         <v>295</v>
       </c>
-      <c r="B299" s="9">
+      <c r="B299" s="6">
         <v>201.6</v>
       </c>
     </row>
@@ -3418,7 +3546,7 @@
       <c r="A300">
         <v>296</v>
       </c>
-      <c r="B300" s="9">
+      <c r="B300" s="6">
         <v>14.8</v>
       </c>
     </row>
@@ -3426,7 +3554,7 @@
       <c r="A301">
         <v>297</v>
       </c>
-      <c r="B301" s="9">
+      <c r="B301" s="6">
         <v>57.7</v>
       </c>
     </row>
@@ -3434,7 +3562,7 @@
       <c r="A302">
         <v>298</v>
       </c>
-      <c r="B302" s="9">
+      <c r="B302" s="6">
         <v>7.2</v>
       </c>
     </row>
@@ -3442,7 +3570,7 @@
       <c r="A303">
         <v>299</v>
       </c>
-      <c r="B303" s="9">
+      <c r="B303" s="6">
         <v>31.1</v>
       </c>
     </row>
@@ -3450,7 +3578,7 @@
       <c r="A304">
         <v>300</v>
       </c>
-      <c r="B304" s="9">
+      <c r="B304" s="6">
         <v>169.4</v>
       </c>
     </row>
@@ -3458,7 +3586,7 @@
       <c r="A305">
         <v>301</v>
       </c>
-      <c r="B305" s="9">
+      <c r="B305" s="6">
         <v>10.7</v>
       </c>
     </row>
@@ -3466,7 +3594,7 @@
       <c r="A306">
         <v>302</v>
       </c>
-      <c r="B306" s="9">
+      <c r="B306" s="6">
         <v>132.6</v>
       </c>
     </row>
@@ -3474,7 +3602,7 @@
       <c r="A307">
         <v>303</v>
       </c>
-      <c r="B307" s="9">
+      <c r="B307" s="6">
         <v>5.5</v>
       </c>
     </row>
@@ -3482,7 +3610,7 @@
       <c r="A308">
         <v>304</v>
       </c>
-      <c r="B308" s="9">
+      <c r="B308" s="6">
         <v>42</v>
       </c>
     </row>
@@ -3490,7 +3618,7 @@
       <c r="A309">
         <v>305</v>
       </c>
-      <c r="B309" s="9">
+      <c r="B309" s="6">
         <v>12.4</v>
       </c>
     </row>
@@ -3498,7 +3626,7 @@
       <c r="A310">
         <v>306</v>
       </c>
-      <c r="B310" s="9">
+      <c r="B310" s="6">
         <v>38.799999999999997</v>
       </c>
     </row>
@@ -3506,7 +3634,7 @@
       <c r="A311">
         <v>307</v>
       </c>
-      <c r="B311" s="9">
+      <c r="B311" s="6">
         <v>30.8</v>
       </c>
     </row>
@@ -3514,7 +3642,7 @@
       <c r="A312">
         <v>308</v>
       </c>
-      <c r="B312" s="9">
+      <c r="B312" s="6">
         <v>92.9</v>
       </c>
     </row>
@@ -3522,7 +3650,7 @@
       <c r="A313">
         <v>309</v>
       </c>
-      <c r="B313" s="9">
+      <c r="B313" s="6">
         <v>52.6</v>
       </c>
     </row>
@@ -3530,7 +3658,7 @@
       <c r="A314">
         <v>310</v>
       </c>
-      <c r="B314" s="9">
+      <c r="B314" s="6">
         <v>47.2</v>
       </c>
     </row>
@@ -3538,7 +3666,7 @@
       <c r="A315">
         <v>311</v>
       </c>
-      <c r="B315" s="9">
+      <c r="B315" s="6">
         <v>22.4</v>
       </c>
     </row>
@@ -3546,7 +3674,7 @@
       <c r="A316">
         <v>312</v>
       </c>
-      <c r="B316" s="9">
+      <c r="B316" s="6">
         <v>63.3</v>
       </c>
     </row>
@@ -3554,7 +3682,7 @@
       <c r="A317">
         <v>313</v>
       </c>
-      <c r="B317" s="9">
+      <c r="B317" s="6">
         <v>17.100000000000001</v>
       </c>
     </row>
@@ -3562,7 +3690,7 @@
       <c r="A318">
         <v>314</v>
       </c>
-      <c r="B318" s="9">
+      <c r="B318" s="6">
         <v>20.2</v>
       </c>
     </row>
@@ -3570,7 +3698,7 @@
       <c r="A319">
         <v>315</v>
       </c>
-      <c r="B319" s="9">
+      <c r="B319" s="6">
         <v>20.5</v>
       </c>
     </row>
@@ -3578,7 +3706,7 @@
       <c r="A320">
         <v>316</v>
       </c>
-      <c r="B320" s="9">
+      <c r="B320" s="6">
         <v>71.8</v>
       </c>
     </row>
@@ -3586,7 +3714,7 @@
       <c r="A321">
         <v>317</v>
       </c>
-      <c r="B321" s="9">
+      <c r="B321" s="6">
         <v>424.5</v>
       </c>
     </row>
@@ -3594,7 +3722,7 @@
       <c r="A322">
         <v>318</v>
       </c>
-      <c r="B322" s="9">
+      <c r="B322" s="6">
         <v>37</v>
       </c>
     </row>
@@ -3602,7 +3730,7 @@
       <c r="A323">
         <v>319</v>
       </c>
-      <c r="B323" s="9">
+      <c r="B323" s="6">
         <v>296.7</v>
       </c>
     </row>
@@ -3610,7 +3738,7 @@
       <c r="A324">
         <v>320</v>
       </c>
-      <c r="B324" s="9">
+      <c r="B324" s="6">
         <v>13.6</v>
       </c>
     </row>
@@ -3618,7 +3746,7 @@
       <c r="A325">
         <v>321</v>
       </c>
-      <c r="B325" s="9">
+      <c r="B325" s="6">
         <v>21.2</v>
       </c>
     </row>
@@ -3626,7 +3754,7 @@
       <c r="A326">
         <v>322</v>
       </c>
-      <c r="B326" s="9">
+      <c r="B326" s="6">
         <v>68.400000000000006</v>
       </c>
     </row>
@@ -3634,7 +3762,7 @@
       <c r="A327">
         <v>323</v>
       </c>
-      <c r="B327" s="9">
+      <c r="B327" s="6">
         <v>75</v>
       </c>
     </row>
@@ -3642,7 +3770,7 @@
       <c r="A328">
         <v>324</v>
       </c>
-      <c r="B328" s="9">
+      <c r="B328" s="6">
         <v>88.1</v>
       </c>
     </row>
@@ -3650,7 +3778,7 @@
       <c r="A329">
         <v>325</v>
       </c>
-      <c r="B329" s="9">
+      <c r="B329" s="6">
         <v>207.4</v>
       </c>
     </row>
@@ -3658,7 +3786,7 @@
       <c r="A330">
         <v>326</v>
       </c>
-      <c r="B330" s="9">
+      <c r="B330" s="6">
         <v>32.1</v>
       </c>
     </row>
@@ -3666,7 +3794,7 @@
       <c r="A331">
         <v>327</v>
       </c>
-      <c r="B331" s="9">
+      <c r="B331" s="6">
         <v>123.8</v>
       </c>
     </row>
@@ -3674,7 +3802,7 @@
       <c r="A332">
         <v>328</v>
       </c>
-      <c r="B332" s="9">
+      <c r="B332" s="6">
         <v>51.5</v>
       </c>
     </row>
@@ -3682,7 +3810,7 @@
       <c r="A333">
         <v>329</v>
       </c>
-      <c r="B333" s="9">
+      <c r="B333" s="6">
         <v>2.1</v>
       </c>
     </row>
@@ -3690,7 +3818,7 @@
       <c r="A334">
         <v>330</v>
       </c>
-      <c r="B334" s="9">
+      <c r="B334" s="6">
         <v>14</v>
       </c>
     </row>
@@ -3698,7 +3826,7 @@
       <c r="A335">
         <v>331</v>
       </c>
-      <c r="B335" s="9">
+      <c r="B335" s="6">
         <v>22.9</v>
       </c>
     </row>
@@ -3706,7 +3834,7 @@
       <c r="A336">
         <v>332</v>
       </c>
-      <c r="B336" s="9">
+      <c r="B336" s="6">
         <v>44.8</v>
       </c>
     </row>
@@ -3714,7 +3842,7 @@
       <c r="A337">
         <v>333</v>
       </c>
-      <c r="B337" s="9">
+      <c r="B337" s="6">
         <v>69.5</v>
       </c>
     </row>
@@ -3722,7 +3850,7 @@
       <c r="A338">
         <v>334</v>
       </c>
-      <c r="B338" s="9">
+      <c r="B338" s="6">
         <v>29.9</v>
       </c>
     </row>
@@ -3730,7 +3858,7 @@
       <c r="A339">
         <v>335</v>
       </c>
-      <c r="B339" s="9">
+      <c r="B339" s="6">
         <v>157.80000000000001</v>
       </c>
     </row>
@@ -3738,7 +3866,7 @@
       <c r="A340">
         <v>336</v>
       </c>
-      <c r="B340" s="9">
+      <c r="B340" s="6">
         <v>14.4</v>
       </c>
     </row>
@@ -3746,7 +3874,7 @@
       <c r="A341">
         <v>337</v>
       </c>
-      <c r="B341" s="9">
+      <c r="B341" s="6">
         <v>38.9</v>
       </c>
     </row>
@@ -3754,7 +3882,7 @@
       <c r="A342">
         <v>338</v>
       </c>
-      <c r="B342" s="9">
+      <c r="B342" s="6">
         <v>104.7</v>
       </c>
     </row>
@@ -3762,7 +3890,7 @@
       <c r="A343">
         <v>339</v>
       </c>
-      <c r="B343" s="9">
+      <c r="B343" s="6">
         <v>12.3</v>
       </c>
     </row>
@@ -3770,7 +3898,7 @@
       <c r="A344">
         <v>340</v>
       </c>
-      <c r="B344" s="9">
+      <c r="B344" s="6">
         <v>148.9</v>
       </c>
     </row>
@@ -3778,7 +3906,7 @@
       <c r="A345">
         <v>341</v>
       </c>
-      <c r="B345" s="9">
+      <c r="B345" s="6">
         <v>108.4</v>
       </c>
     </row>
@@ -3786,7 +3914,7 @@
       <c r="A346">
         <v>342</v>
       </c>
-      <c r="B346" s="9">
+      <c r="B346" s="6">
         <v>33.700000000000003</v>
       </c>
     </row>
@@ -3794,7 +3922,7 @@
       <c r="A347">
         <v>343</v>
       </c>
-      <c r="B347" s="9">
+      <c r="B347" s="6">
         <v>40.1</v>
       </c>
     </row>
@@ -3802,7 +3930,7 @@
       <c r="A348">
         <v>344</v>
       </c>
-      <c r="B348" s="9">
+      <c r="B348" s="6">
         <v>36.4</v>
       </c>
     </row>
@@ -3810,7 +3938,7 @@
       <c r="A349">
         <v>345</v>
       </c>
-      <c r="B349" s="9">
+      <c r="B349" s="6">
         <v>40.799999999999997</v>
       </c>
     </row>
@@ -3818,7 +3946,7 @@
       <c r="A350">
         <v>346</v>
       </c>
-      <c r="B350" s="9">
+      <c r="B350" s="6">
         <v>147.4</v>
       </c>
     </row>
@@ -3826,7 +3954,7 @@
       <c r="A351">
         <v>347</v>
       </c>
-      <c r="B351" s="9">
+      <c r="B351" s="6">
         <v>68.5</v>
       </c>
     </row>
@@ -3834,7 +3962,7 @@
       <c r="A352">
         <v>348</v>
       </c>
-      <c r="B352" s="9">
+      <c r="B352" s="6">
         <v>9.4</v>
       </c>
     </row>
@@ -3842,7 +3970,7 @@
       <c r="A353">
         <v>349</v>
       </c>
-      <c r="B353" s="9">
+      <c r="B353" s="6">
         <v>7.9</v>
       </c>
     </row>
@@ -3850,7 +3978,7 @@
       <c r="A354">
         <v>350</v>
       </c>
-      <c r="B354" s="9">
+      <c r="B354" s="6">
         <v>75</v>
       </c>
     </row>
@@ -3858,7 +3986,7 @@
       <c r="A355">
         <v>351</v>
       </c>
-      <c r="B355" s="9">
+      <c r="B355" s="6">
         <v>2.5</v>
       </c>
     </row>
@@ -3866,7 +3994,7 @@
       <c r="A356">
         <v>352</v>
       </c>
-      <c r="B356" s="9">
+      <c r="B356" s="6">
         <v>7.6</v>
       </c>
     </row>
@@ -3874,7 +4002,7 @@
       <c r="A357">
         <v>353</v>
       </c>
-      <c r="B357" s="9">
+      <c r="B357" s="6">
         <v>20.9</v>
       </c>
     </row>
@@ -3882,7 +4010,7 @@
       <c r="A358">
         <v>354</v>
       </c>
-      <c r="B358" s="9">
+      <c r="B358" s="6">
         <v>38.700000000000003</v>
       </c>
     </row>
@@ -3890,7 +4018,7 @@
       <c r="A359">
         <v>355</v>
       </c>
-      <c r="B359" s="9">
+      <c r="B359" s="6">
         <v>163</v>
       </c>
     </row>
@@ -3898,7 +4026,7 @@
       <c r="A360">
         <v>356</v>
       </c>
-      <c r="B360" s="9">
+      <c r="B360" s="6">
         <v>47.6</v>
       </c>
     </row>
@@ -3906,7 +4034,7 @@
       <c r="A361">
         <v>357</v>
       </c>
-      <c r="B361" s="9">
+      <c r="B361" s="6">
         <v>1568.3</v>
       </c>
     </row>
@@ -3914,7 +4042,7 @@
       <c r="A362">
         <v>358</v>
       </c>
-      <c r="B362" s="9">
+      <c r="B362" s="6">
         <v>49.4</v>
       </c>
     </row>
@@ -3922,7 +4050,7 @@
       <c r="A363">
         <v>359</v>
       </c>
-      <c r="B363" s="9">
+      <c r="B363" s="6">
         <v>96.8</v>
       </c>
     </row>
@@ -3930,7 +4058,7 @@
       <c r="A364">
         <v>360</v>
       </c>
-      <c r="B364" s="9">
+      <c r="B364" s="6">
         <v>114.3</v>
       </c>
     </row>
@@ -3938,7 +4066,7 @@
       <c r="A365">
         <v>361</v>
       </c>
-      <c r="B365" s="9">
+      <c r="B365" s="6">
         <v>35.200000000000003</v>
       </c>
     </row>
@@ -3946,7 +4074,7 @@
       <c r="A366">
         <v>362</v>
       </c>
-      <c r="B366" s="9">
+      <c r="B366" s="6">
         <v>106.9</v>
       </c>
     </row>
@@ -3954,7 +4082,7 @@
       <c r="A367">
         <v>363</v>
       </c>
-      <c r="B367" s="9">
+      <c r="B367" s="6">
         <v>73.5</v>
       </c>
     </row>
@@ -3962,7 +4090,7 @@
       <c r="A368">
         <v>364</v>
       </c>
-      <c r="B368" s="9">
+      <c r="B368" s="6">
         <v>50.4</v>
       </c>
     </row>
@@ -3970,7 +4098,7 @@
       <c r="A369">
         <v>365</v>
       </c>
-      <c r="B369" s="9">
+      <c r="B369" s="6">
         <v>20.3</v>
       </c>
     </row>
@@ -3978,7 +4106,7 @@
       <c r="A370">
         <v>366</v>
       </c>
-      <c r="B370" s="9">
+      <c r="B370" s="6">
         <v>25.1</v>
       </c>
     </row>
@@ -3986,7 +4114,7 @@
       <c r="A371">
         <v>367</v>
       </c>
-      <c r="B371" s="9">
+      <c r="B371" s="6">
         <v>90.6</v>
       </c>
     </row>
@@ -3994,7 +4122,7 @@
       <c r="A372">
         <v>368</v>
       </c>
-      <c r="B372" s="9">
+      <c r="B372" s="6">
         <v>37.9</v>
       </c>
     </row>
@@ -4002,7 +4130,7 @@
       <c r="A373">
         <v>369</v>
       </c>
-      <c r="B373" s="9">
+      <c r="B373" s="6">
         <v>60</v>
       </c>
     </row>
@@ -4010,7 +4138,7 @@
       <c r="A374">
         <v>370</v>
       </c>
-      <c r="B374" s="9">
+      <c r="B374" s="6">
         <v>60</v>
       </c>
     </row>
@@ -4018,7 +4146,7 @@
       <c r="A375">
         <v>371</v>
       </c>
-      <c r="B375" s="9">
+      <c r="B375" s="6">
         <v>52.6</v>
       </c>
     </row>
@@ -4026,7 +4154,7 @@
       <c r="A376">
         <v>372</v>
       </c>
-      <c r="B376" s="9">
+      <c r="B376" s="6">
         <v>39.9</v>
       </c>
     </row>
@@ -4034,7 +4162,7 @@
       <c r="A377">
         <v>373</v>
       </c>
-      <c r="B377" s="9">
+      <c r="B377" s="6">
         <v>72.8</v>
       </c>
     </row>
@@ -4042,7 +4170,7 @@
       <c r="A378">
         <v>374</v>
       </c>
-      <c r="B378" s="9">
+      <c r="B378" s="6">
         <v>93.9</v>
       </c>
     </row>
@@ -4050,7 +4178,7 @@
       <c r="A379">
         <v>375</v>
       </c>
-      <c r="B379" s="9">
+      <c r="B379" s="6">
         <v>166</v>
       </c>
     </row>
@@ -4058,7 +4186,7 @@
       <c r="A380">
         <v>376</v>
       </c>
-      <c r="B380" s="9">
+      <c r="B380" s="6">
         <v>66.400000000000006</v>
       </c>
     </row>
@@ -4066,7 +4194,7 @@
       <c r="A381">
         <v>377</v>
       </c>
-      <c r="B381" s="9">
+      <c r="B381" s="6">
         <v>21.8</v>
       </c>
     </row>
@@ -4074,7 +4202,7 @@
       <c r="A382">
         <v>378</v>
       </c>
-      <c r="B382" s="9">
+      <c r="B382" s="6">
         <v>19.399999999999999</v>
       </c>
     </row>
@@ -4082,7 +4210,7 @@
       <c r="A383">
         <v>379</v>
       </c>
-      <c r="B383" s="9">
+      <c r="B383" s="6">
         <v>76.7</v>
       </c>
     </row>
@@ -4090,7 +4218,7 @@
       <c r="A384">
         <v>380</v>
       </c>
-      <c r="B384" s="9">
+      <c r="B384" s="6">
         <v>8</v>
       </c>
     </row>
@@ -4098,7 +4226,7 @@
       <c r="A385">
         <v>381</v>
       </c>
-      <c r="B385" s="9">
+      <c r="B385" s="6">
         <v>22.8</v>
       </c>
     </row>
@@ -4106,7 +4234,7 @@
       <c r="A386">
         <v>382</v>
       </c>
-      <c r="B386" s="9">
+      <c r="B386" s="6">
         <v>117</v>
       </c>
     </row>
@@ -4114,7 +4242,7 @@
       <c r="A387">
         <v>383</v>
       </c>
-      <c r="B387" s="9">
+      <c r="B387" s="6">
         <v>27.8</v>
       </c>
     </row>
@@ -4122,7 +4250,7 @@
       <c r="A388">
         <v>384</v>
       </c>
-      <c r="B388" s="9">
+      <c r="B388" s="6">
         <v>19.8</v>
       </c>
     </row>
@@ -4130,7 +4258,7 @@
       <c r="A389">
         <v>385</v>
       </c>
-      <c r="B389" s="9">
+      <c r="B389" s="6">
         <v>143</v>
       </c>
     </row>
@@ -4138,7 +4266,7 @@
       <c r="A390">
         <v>386</v>
       </c>
-      <c r="B390" s="9">
+      <c r="B390" s="6">
         <v>2.4</v>
       </c>
     </row>
@@ -4146,7 +4274,7 @@
       <c r="A391">
         <v>387</v>
       </c>
-      <c r="B391" s="9">
+      <c r="B391" s="6">
         <v>36.299999999999997</v>
       </c>
     </row>
@@ -4154,7 +4282,7 @@
       <c r="A392">
         <v>388</v>
       </c>
-      <c r="B392" s="9">
+      <c r="B392" s="6">
         <v>24.4</v>
       </c>
     </row>
@@ -4162,7 +4290,7 @@
       <c r="A393">
         <v>389</v>
       </c>
-      <c r="B393" s="9">
+      <c r="B393" s="6">
         <v>23.6</v>
       </c>
     </row>
@@ -4170,7 +4298,7 @@
       <c r="A394">
         <v>390</v>
       </c>
-      <c r="B394" s="9">
+      <c r="B394" s="6">
         <v>101.8</v>
       </c>
     </row>
@@ -4178,7 +4306,7 @@
       <c r="A395">
         <v>391</v>
       </c>
-      <c r="B395" s="9">
+      <c r="B395" s="6">
         <v>189.1</v>
       </c>
     </row>
@@ -4186,7 +4314,7 @@
       <c r="A396">
         <v>392</v>
       </c>
-      <c r="B396" s="9">
+      <c r="B396" s="6">
         <v>128.9</v>
       </c>
     </row>
@@ -4194,7 +4322,7 @@
       <c r="A397">
         <v>393</v>
       </c>
-      <c r="B397" s="9">
+      <c r="B397" s="6">
         <v>75.5</v>
       </c>
     </row>
@@ -4202,7 +4330,7 @@
       <c r="A398">
         <v>394</v>
       </c>
-      <c r="B398" s="9">
+      <c r="B398" s="6">
         <v>55.3</v>
       </c>
     </row>
@@ -4210,7 +4338,7 @@
       <c r="A399">
         <v>395</v>
       </c>
-      <c r="B399" s="9">
+      <c r="B399" s="6">
         <v>30.5</v>
       </c>
     </row>
@@ -4218,7 +4346,7 @@
       <c r="A400">
         <v>396</v>
       </c>
-      <c r="B400" s="9">
+      <c r="B400" s="6">
         <v>39.5</v>
       </c>
     </row>
@@ -4226,7 +4354,7 @@
       <c r="A401">
         <v>397</v>
       </c>
-      <c r="B401" s="9">
+      <c r="B401" s="6">
         <v>7.2</v>
       </c>
     </row>
@@ -4234,7 +4362,7 @@
       <c r="A402">
         <v>398</v>
       </c>
-      <c r="B402" s="9">
+      <c r="B402" s="6">
         <v>22.8</v>
       </c>
     </row>
@@ -4242,7 +4370,7 @@
       <c r="A403">
         <v>399</v>
       </c>
-      <c r="B403" s="9">
+      <c r="B403" s="6">
         <v>73.5</v>
       </c>
     </row>
@@ -4250,7 +4378,7 @@
       <c r="A404">
         <v>400</v>
       </c>
-      <c r="B404" s="9">
+      <c r="B404" s="6">
         <v>34.700000000000003</v>
       </c>
     </row>
@@ -4258,7 +4386,7 @@
       <c r="A405">
         <v>401</v>
       </c>
-      <c r="B405" s="9">
+      <c r="B405" s="6">
         <v>93.3</v>
       </c>
     </row>
@@ -4266,7 +4394,7 @@
       <c r="A406">
         <v>402</v>
       </c>
-      <c r="B406" s="9">
+      <c r="B406" s="6">
         <v>7.7</v>
       </c>
     </row>
@@ -4274,7 +4402,7 @@
       <c r="A407">
         <v>403</v>
       </c>
-      <c r="B407" s="9">
+      <c r="B407" s="6">
         <v>21.9</v>
       </c>
     </row>
@@ -4282,7 +4410,7 @@
       <c r="A408">
         <v>404</v>
       </c>
-      <c r="B408" s="9">
+      <c r="B408" s="6">
         <v>13.8</v>
       </c>
     </row>
@@ -4290,7 +4418,7 @@
       <c r="A409">
         <v>405</v>
       </c>
-      <c r="B409" s="9">
+      <c r="B409" s="6">
         <v>118.4</v>
       </c>
     </row>
@@ -4298,7 +4426,7 @@
       <c r="A410">
         <v>406</v>
       </c>
-      <c r="B410" s="9">
+      <c r="B410" s="6">
         <v>29.9</v>
       </c>
     </row>
@@ -4306,7 +4434,7 @@
       <c r="A411">
         <v>407</v>
       </c>
-      <c r="B411" s="9">
+      <c r="B411" s="6">
         <v>28.9</v>
       </c>
     </row>
@@ -4314,7 +4442,7 @@
       <c r="A412">
         <v>408</v>
       </c>
-      <c r="B412" s="9">
+      <c r="B412" s="6">
         <v>10.9</v>
       </c>
     </row>
@@ -4322,7 +4450,7 @@
       <c r="A413">
         <v>409</v>
       </c>
-      <c r="B413" s="9">
+      <c r="B413" s="6">
         <v>23.2</v>
       </c>
     </row>
@@ -4330,7 +4458,7 @@
       <c r="A414">
         <v>410</v>
       </c>
-      <c r="B414" s="9">
+      <c r="B414" s="6">
         <v>13.7</v>
       </c>
     </row>
@@ -4338,7 +4466,7 @@
       <c r="A415">
         <v>411</v>
       </c>
-      <c r="B415" s="9">
+      <c r="B415" s="6">
         <v>21.7</v>
       </c>
     </row>
@@ -4346,7 +4474,7 @@
       <c r="A416">
         <v>412</v>
       </c>
-      <c r="B416" s="9">
+      <c r="B416" s="6">
         <v>382</v>
       </c>
     </row>
@@ -4354,7 +4482,7 @@
       <c r="A417">
         <v>413</v>
       </c>
-      <c r="B417" s="9">
+      <c r="B417" s="6">
         <v>11.8</v>
       </c>
     </row>
@@ -4362,7 +4490,7 @@
       <c r="A418">
         <v>414</v>
       </c>
-      <c r="B418" s="9">
+      <c r="B418" s="6">
         <v>29.9</v>
       </c>
     </row>
@@ -4370,7 +4498,7 @@
       <c r="A419">
         <v>415</v>
       </c>
-      <c r="B419" s="9">
+      <c r="B419" s="6">
         <v>15.4</v>
       </c>
     </row>
@@ -4378,7 +4506,7 @@
       <c r="A420">
         <v>416</v>
       </c>
-      <c r="B420" s="9">
+      <c r="B420" s="6">
         <v>153.80000000000001</v>
       </c>
     </row>
@@ -4386,7 +4514,7 @@
       <c r="A421">
         <v>417</v>
       </c>
-      <c r="B421" s="9">
+      <c r="B421" s="6">
         <v>14.2</v>
       </c>
     </row>
@@ -4394,7 +4522,7 @@
       <c r="A422">
         <v>418</v>
       </c>
-      <c r="B422" s="9">
+      <c r="B422" s="6">
         <v>15.8</v>
       </c>
     </row>
@@ -4402,7 +4530,7 @@
       <c r="A423">
         <v>419</v>
       </c>
-      <c r="B423" s="9">
+      <c r="B423" s="6">
         <v>57.4</v>
       </c>
     </row>
@@ -4410,7 +4538,7 @@
       <c r="A424">
         <v>420</v>
       </c>
-      <c r="B424" s="9">
+      <c r="B424" s="6">
         <v>221.6</v>
       </c>
     </row>
@@ -4436,110 +4564,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="A1" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="A2" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="6" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+        <v>53</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="10">
+        <v>55</v>
+      </c>
+      <c r="B8" s="7">
         <v>60</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="C8" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="A10" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+        <v>58</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/examples/demos/09_tail_risk_op_losses.xlsx
+++ b/examples/demos/09_tail_risk_op_losses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21C7ACB-7EBC-4882-9A77-D0272E5DF3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955425B-7D30-4C5B-B4DD-D0C77973F43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
     <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
   </si>
   <si>
-    <t>PROMPT →  Using this workbook: fit distributions to all losses in 'Data'!B5:B424 and rank them; fit a GPD tail to the exceedances in 'Data'!D5:D44 and write the fitted object into Model!B6, reporting the tail's P99 and P99.9 analytically; build an annual aggregate in Model!B11 (frequency VosePoisson(60), severity = the best-fit body distribution, Monte Carlo method); write =B11 into Model!B13 wrapped as output "OpLoss"; run 10,000 iterations; and give me the 99.9% VaR and CVaR of OpLoss — the capital requirement.</t>
+    <t>PROMPT →  Using this workbook: fit distributions to all losses in 'Data'!B5:B424 and rank them; fit a GPD tail to the exceedances in 'Data'!D5:D44 and write the fitted object into Model!B6, reporting the tail's P99 and P99.9 analytically; build an annual aggregate in Model!B11 (frequency VosePoisson(60) (put the frequency object in Model!B30 and the severity object in Model!B31 — they are safely outside the merged note rows), severity = the best-fit body distribution, Monte Carlo method); write =B11 into Model!B13 wrapped as output "OpLoss"; run 10,000 iterations; and give me the 99.9% VaR and CVaR of OpLoss — the capital requirement.</t>
   </si>
   <si>
     <t>Expected: body fit + GPD tail + a simulated 99.9% capital number, in one pass.</t>
@@ -111,7 +111,7 @@
     <t>Annual capital model — combine frequency and severity into an annual aggregate and simulate.</t>
   </si>
   <si>
-    <t>PROMPT →  Build an annual aggregate in Model!B11: frequency VosePoisson(60), severity = the best-fit body distribution, Monte Carlo method; write =B11 into B13 wrapped as output "OpLoss"; then run 10,000 iterations.</t>
+    <t>PROMPT →  Build an annual aggregate in Model!B11: frequency VosePoisson(60) (put the frequency object in Model!B30 and the severity object in Model!B31 — they are safely outside the merged note rows), severity = the best-fit body distribution, Monte Carlo method; write =B11 into B13 wrapped as output "OpLoss"; then run 10,000 iterations.</t>
   </si>
   <si>
     <t>Expected: B11 gets an aggregate MC object, B13 becomes the simulation output 'OpLoss', and a 10,000-iteration run completes.</t>
@@ -392,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -419,13 +419,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -747,16 +745,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15" t="s">
@@ -979,7 +977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="14"/>
       <c r="B53" s="8" t="s">
         <v>41</v>
@@ -1022,28 +1020,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
@@ -4564,54 +4562,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
@@ -4620,54 +4618,54 @@
       <c r="B8" s="7">
         <v>60</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/examples/demos/09_tail_risk_op_losses.xlsx
+++ b/examples/demos/09_tail_risk_op_losses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955425B-7D30-4C5B-B4DD-D0C77973F43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240B30C8-152E-4D27-9F0D-72E81D33D125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,12 +418,12 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -745,19 +745,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="16"/>
@@ -778,7 +778,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="16"/>
@@ -804,7 +804,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="16"/>
@@ -825,7 +825,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="17" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="16"/>
@@ -939,7 +939,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B45" s="16"/>
@@ -960,7 +960,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B50" s="16"/>
